--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104641_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104641_W21.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4017</v>
+        <v>4.0705</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5486</v>
+        <v>2.4545</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8532</v>
+        <v>1.616</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3638</v>
+        <v>3.368</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2523</v>
+        <v>2.2599</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1115</v>
+        <v>1.1081</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8735</v>
+        <v>4.8408</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9785</v>
+        <v>2.9647</v>
       </c>
       <c r="L2" t="n">
-        <v>1.895</v>
+        <v>1.8761</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5097</v>
+        <v>-1.4728</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7261</v>
+        <v>-0.7048</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7835</v>
+        <v>-0.768</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4177</v>
+        <v>-0.7513</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.378</v>
+        <v>-0.4255</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0397</v>
+        <v>-0.3257</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4387</v>
+        <v>3.3161</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7753</v>
+        <v>2.8831</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6634</v>
+        <v>0.433</v>
       </c>
       <c r="G3" t="n">
-        <v>3.43</v>
+        <v>3.4306</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8066</v>
+        <v>1.8038</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6233</v>
+        <v>1.6268</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9658</v>
+        <v>2.9553</v>
       </c>
       <c r="K3" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4641</v>
+        <v>0.4754</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>0.196</v>
+        <v>0.0629</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1905</v>
+        <v>-0.0721</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3865</v>
+        <v>0.135</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2995</v>
+        <v>2.6567</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8609</v>
+        <v>3.0684</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5614</v>
+        <v>-0.4117</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7639</v>
+        <v>1.7568</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6783</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0769</v>
+        <v>1.0786</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4155</v>
+        <v>3.3907</v>
       </c>
       <c r="K4" t="n">
-        <v>1.475</v>
+        <v>1.4544</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9405</v>
+        <v>1.9363</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6516</v>
+        <v>-1.6339</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2129</v>
+        <v>0.1487</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3297</v>
+        <v>-0.0931</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1167</v>
+        <v>0.2418</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0527</v>
+        <v>1.4022</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0634</v>
+        <v>1.3773</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0107</v>
+        <v>0.0249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8324</v>
+        <v>0.8182</v>
       </c>
       <c r="H5" t="n">
-        <v>0.358</v>
+        <v>0.3508</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4744</v>
+        <v>0.4674</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3503</v>
+        <v>2.307</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0523</v>
+        <v>1.0267</v>
       </c>
       <c r="L5" t="n">
-        <v>1.298</v>
+        <v>1.2803</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5179</v>
+        <v>-1.4888</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6944</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4718</v>
+        <v>-0.1672</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6866</v>
+        <v>0.0507</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2148</v>
+        <v>-0.2179</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. NZOSA</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3917</v>
+        <v>0.9156</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1914</v>
+        <v>1.0193</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5831</v>
+        <v>-0.1036</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6464</v>
+        <v>0.1472</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3319</v>
+        <v>2.2003</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3145</v>
+        <v>-2.0531</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0173</v>
+        <v>2.2501</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0173</v>
+        <v>3.2643</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.0142</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6291</v>
+        <v>-2.1029</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3145</v>
+        <v>-1.064</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3145</v>
+        <v>-1.0389</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>2.5039</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2268</v>
+        <v>3.8697</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4815</v>
+        <v>-1.5063</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2087</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2728</v>
+        <v>-0.781</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2292</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8603</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>Y. NZOSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3907</v>
+        <v>0.6443</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0182</v>
+        <v>-0.0037</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6274999999999999</v>
+        <v>0.648</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1604</v>
+        <v>0.649</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2049</v>
+        <v>0.3331</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0445</v>
+        <v>0.3159</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3068</v>
+        <v>0.0172</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2933</v>
+        <v>0.0172</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9865</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1464</v>
+        <v>0.6317</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0884</v>
+        <v>0.3159</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0581</v>
+        <v>0.3159</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4952</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.8562</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.04</v>
+        <v>-0.2323</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7954</v>
+        <v>-0.021</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2446</v>
+        <v>-0.2113</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8678</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4671</v>
+        <v>-0.3708</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8018</v>
+        <v>-0.8094</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3347</v>
+        <v>0.4386</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9516</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5945</v>
+        <v>-0.5972</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3572</v>
+        <v>-0.3544</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1576</v>
+        <v>-0.1636</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2322</v>
+        <v>-0.2381</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.794</v>
+        <v>-0.7881</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3548</v>
+        <v>-0.2614</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4174</v>
+        <v>-0.4182</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0626</v>
+        <v>0.1568</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. DIEZ</t>
+          <t>J. TABOADA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5917</v>
+        <v>-0.4255</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4872</v>
+        <v>2.6567</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1046</v>
+        <v>-3.0822</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4797</v>
+        <v>2.3448</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1414</v>
+        <v>0.2236</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6211</v>
+        <v>2.1212</v>
       </c>
       <c r="J9" t="n">
-        <v>0.157</v>
+        <v>3.1168</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3463</v>
+        <v>0.1379</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1893</v>
+        <v>2.9789</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6368</v>
+        <v>-0.772</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.205</v>
+        <v>0.0857</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4318</v>
+        <v>-0.8578</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.405</v>
+        <v>-0.7782</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4174</v>
+        <v>-0.4601</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0124</v>
+        <v>-0.3181</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1607</v>
+        <v>-3.8132</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. TABOADA</t>
+          <t>D. DIEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9406</v>
+        <v>-0.5011</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3587</v>
+        <v>-0.3765</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.2993</v>
+        <v>-0.1246</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3381</v>
+        <v>-0.4792</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2163</v>
+        <v>0.1435</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1218</v>
+        <v>-0.6227</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1239</v>
+        <v>0.1509</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1385</v>
+        <v>0.3447</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9853</v>
+        <v>-0.1939</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.6301</v>
       </c>
       <c r="N10" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.2012</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8636</v>
+        <v>-0.4289</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.269</v>
+        <v>-0.3194</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7652</v>
+        <v>-0.2998</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5039</v>
+        <v>-0.0196</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.8243</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.8243</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2079</v>
+        <v>-1.8866</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2305</v>
+        <v>-1.6305</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0226</v>
+        <v>-0.2561</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7588</v>
+        <v>1.7497</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1186</v>
+        <v>2.0978</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3598</v>
+        <v>-0.3481</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7255</v>
+        <v>2.6925</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5762</v>
+        <v>2.5436</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9666</v>
+        <v>-0.9428</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R11" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4204</v>
+        <v>-1.0916</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3266</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.4107</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4482</v>
+        <v>-2.1558</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6134</v>
+        <v>-3.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1653</v>
+        <v>1.1442</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9245</v>
+        <v>-0.9184</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0231</v>
+        <v>-1.0198</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1057</v>
+        <v>0.0822</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1874</v>
+        <v>-0.2003</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2931</v>
+        <v>0.2826</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0302</v>
+        <v>-1.0006</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6145</v>
+        <v>-1.3285</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1825</v>
+        <v>-0.8296</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4319</v>
+        <v>-0.4989</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.319499999999998</v>
+        <v>7.6656</v>
       </c>
       <c r="E13" t="n">
-        <v>7.300800000000001</v>
+        <v>7.339200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01879999999999971</v>
+        <v>0.3265000000000002</v>
       </c>
       <c r="G13" t="n">
-        <v>11.938</v>
+        <v>11.9151</v>
       </c>
       <c r="H13" t="n">
-        <v>8.499400000000001</v>
+        <v>8.4741</v>
       </c>
       <c r="I13" t="n">
-        <v>3.438399999999999</v>
+        <v>3.441099999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>21.8837</v>
+        <v>21.6399</v>
       </c>
       <c r="K13" t="n">
-        <v>13.1548</v>
+        <v>13.0043</v>
       </c>
       <c r="L13" t="n">
-        <v>8.728800000000001</v>
+        <v>8.6356</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.945800000000002</v>
+        <v>-9.7249</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.6555</v>
+        <v>-4.5302</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.2904</v>
+        <v>-5.194599999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>7.939400000000001</v>
+        <v>7.967299999999998</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.4757</v>
+        <v>-12.5197</v>
       </c>
       <c r="R13" t="n">
-        <v>20.415</v>
+        <v>20.4869</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.548</v>
+        <v>-6.2246</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.3248</v>
+        <v>-3.9749</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2233</v>
+        <v>-2.2496</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.0097</v>
+        <v>-5.992299999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2177</v>
+        <v>2.1939</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.2273</v>
+        <v>-8.186</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5614</v>
+        <v>2.409</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8176</v>
+        <v>2.7331</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2562</v>
+        <v>-0.3241</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.25</v>
+        <v>-1.246</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.7696</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4824</v>
+        <v>-0.4764</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1907</v>
+        <v>1.1747</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1527</v>
+        <v>-0.1659</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4407</v>
+        <v>-2.4207</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6261</v>
+        <v>1.4761</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8026</v>
+        <v>0.7453</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8235</v>
+        <v>0.7308</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>M. NORMANTAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3704</v>
+        <v>1.96</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4833</v>
+        <v>0.6841</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8536</v>
+        <v>1.2759</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2515</v>
+        <v>1.225</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5181</v>
+        <v>2.4588</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2666</v>
+        <v>-1.2339</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2361</v>
+        <v>2.9006</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4227</v>
+        <v>3.7954</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1866</v>
+        <v>-0.8948</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0153</v>
+        <v>-1.6756</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0954</v>
+        <v>-1.3365</v>
       </c>
       <c r="O15" t="n">
-        <v>0.08</v>
+        <v>-0.3391</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1342</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4952</v>
+        <v>-3.6421</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6633</v>
+        <v>1.0812</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1553</v>
+        <v>0.1784</v>
       </c>
       <c r="U15" t="n">
-        <v>1.508</v>
+        <v>0.9028</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. NORMANTAS</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.766</v>
+        <v>1.2746</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.314</v>
+        <v>1.1319</v>
       </c>
       <c r="F16" t="n">
-        <v>1.08</v>
+        <v>0.1427</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2411</v>
+        <v>1.3794</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4647</v>
+        <v>-2.2236</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2236</v>
+        <v>3.603</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9481</v>
+        <v>3.4707</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8199</v>
+        <v>-0.5278</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8718</v>
+        <v>3.9986</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.707</v>
+        <v>-2.0913</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3552</v>
+        <v>-1.6957</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3517</v>
+        <v>-0.3956</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.6293</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1406</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8861</v>
+        <v>0.1667</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.5707</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2534</v>
+        <v>-0.387</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2534</v>
+        <v>-0.2292</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2813</v>
+        <v>1.1719</v>
       </c>
       <c r="E17" t="n">
-        <v>1.478</v>
+        <v>-1.2056</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1967</v>
+        <v>2.3775</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1762</v>
+        <v>-0.2383</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7764</v>
+        <v>-0.5143</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3998</v>
+        <v>0.276</v>
       </c>
       <c r="J17" t="n">
-        <v>1.389</v>
+        <v>-0.2415</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2397</v>
+        <v>-0.4277</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>0.1862</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5652</v>
+        <v>0.0032</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0161</v>
+        <v>-0.0866</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.549</v>
+        <v>0.0898</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3006</v>
+        <v>1.4589</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0302</v>
+        <v>0.4504</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3309</v>
+        <v>1.0085</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1568</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1741</v>
+        <v>0.3323</v>
       </c>
       <c r="E18" t="n">
-        <v>0.704</v>
+        <v>1.4568</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5299</v>
+        <v>-1.1245</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3779</v>
+        <v>-1.163</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2339</v>
+        <v>-0.7701</v>
       </c>
       <c r="I18" t="n">
-        <v>3.6117</v>
+        <v>-0.393</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5057</v>
+        <v>1.376</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5164</v>
+        <v>1.2271</v>
       </c>
       <c r="L18" t="n">
-        <v>4.0221</v>
+        <v>0.1489</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1278</v>
+        <v>-2.539</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7175</v>
+        <v>-1.9971</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4104</v>
+        <v>-0.5419</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3644</v>
+        <v>0.3344</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3085</v>
+        <v>-0.0283</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.056</v>
+        <v>0.3627</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3856</v>
+        <v>1.1609</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.2249</v>
+        <v>1.2472</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.0863</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9988</v>
+        <v>-1.5757</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0249</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9739</v>
+        <v>-0.9019</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1479</v>
+        <v>-2.1438</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6898</v>
+        <v>-0.6839</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4581</v>
+        <v>-1.4599</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6771</v>
+        <v>-0.6807</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4708</v>
+        <v>-1.4631</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4633</v>
+        <v>-0.0466</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3478</v>
+        <v>0.0068</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FONT</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0828</v>
+        <v>-1.985</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7211</v>
+        <v>0.4422</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6383</v>
+        <v>-2.4272</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3569</v>
+        <v>-3.4239</v>
       </c>
       <c r="H20" t="n">
-        <v>0.205</v>
+        <v>-3.0798</v>
       </c>
       <c r="I20" t="n">
-        <v>0.152</v>
+        <v>-0.3441</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1914</v>
+        <v>0.2755</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0795</v>
+        <v>-0.5656</v>
       </c>
       <c r="L20" t="n">
-        <v>0.112</v>
+        <v>0.8411</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1655</v>
+        <v>-3.6995</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1255</v>
+        <v>-2.5142</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04</v>
+        <v>-1.1852</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.4952</v>
+        <v>1.1382</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6293</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1481</v>
+        <v>0.4586</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7168</v>
+        <v>0.1667</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4313</v>
+        <v>0.2919</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>A. FONT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7343</v>
+        <v>-2.3133</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0168</v>
+        <v>-3.0936</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7175</v>
+        <v>0.7803</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4407</v>
+        <v>0.3579</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.0969</v>
+        <v>0.2012</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3439</v>
+        <v>0.1566</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2916</v>
+        <v>0.1839</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5612</v>
+        <v>0.0722</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8529</v>
+        <v>0.1117</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.7323</v>
+        <v>0.174</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5356</v>
+        <v>0.129</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1967</v>
+        <v>0.0449</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2671</v>
+        <v>0.9222</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3085</v>
+        <v>0.3646</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0414</v>
+        <v>0.5576</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4241</v>
+        <v>-3.4932</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6057</v>
+        <v>-2.7678</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8184</v>
+        <v>-0.7254</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.2772</v>
+        <v>-4.2874</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6521</v>
+        <v>-0.6601</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.6251</v>
+        <v>-3.6273</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.2875</v>
+        <v>-2.3249</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6714</v>
+        <v>0.6475</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.9588</v>
+        <v>-2.9724</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9897</v>
+        <v>-1.9626</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3234</v>
+        <v>-1.3077</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3729</v>
+        <v>0.3194</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1089</v>
+        <v>-0.0073</v>
       </c>
       <c r="U22" t="n">
-        <v>0.264</v>
+        <v>0.3267</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W22" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2327</v>
+        <v>-4.308</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1476</v>
+        <v>0.9661</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.3804</v>
+        <v>-5.2741</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3704</v>
+        <v>-2.3749</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4343</v>
+        <v>-2.4327</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0639</v>
+        <v>0.0578</v>
       </c>
       <c r="J23" t="n">
-        <v>3.6301</v>
+        <v>3.5905</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4636</v>
+        <v>0.4407</v>
       </c>
       <c r="L23" t="n">
-        <v>3.1665</v>
+        <v>3.1498</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.0004</v>
+        <v>-5.9654</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.8978</v>
+        <v>-2.8734</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.1026</v>
+        <v>-3.092</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6723</v>
+        <v>0.6211</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3206</v>
+        <v>0.2062</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3517</v>
+        <v>0.4149</v>
       </c>
       <c r="V23" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W23" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.319500000000001</v>
+        <v>-6.5274</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.01859999999999951</v>
+        <v>-0.3266999999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.301099999999999</v>
+        <v>-6.2008</v>
       </c>
       <c r="G24" t="n">
-        <v>-11.938</v>
+        <v>-11.915</v>
       </c>
       <c r="H24" t="n">
-        <v>-8.4994</v>
+        <v>-8.4741</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.4387</v>
+        <v>-3.4412</v>
       </c>
       <c r="J24" t="n">
-        <v>9.945900000000002</v>
+        <v>9.724800000000002</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6557</v>
+        <v>4.530399999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>5.2905</v>
+        <v>5.1944</v>
       </c>
       <c r="M24" t="n">
-        <v>-21.8837</v>
+        <v>-21.64</v>
       </c>
       <c r="N24" t="n">
-        <v>-13.1549</v>
+        <v>-13.0043</v>
       </c>
       <c r="O24" t="n">
-        <v>-8.7288</v>
+        <v>-8.6356</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.9392</v>
+        <v>-7.967099999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-20.415</v>
+        <v>-20.4869</v>
       </c>
       <c r="R24" t="n">
-        <v>12.4759</v>
+        <v>12.5199</v>
       </c>
       <c r="S24" t="n">
-        <v>6.5479</v>
+        <v>7.3627</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2231</v>
+        <v>2.2495</v>
       </c>
       <c r="U24" t="n">
-        <v>4.324800000000001</v>
+        <v>5.113199999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>6.0097</v>
+        <v>5.991999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>8.227399999999999</v>
+        <v>8.1858</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.2177</v>
+        <v>-2.1939</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104641_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104641_W21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.186</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.0863</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104641_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-2.1939</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
